--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0002T0006Z000C1N2_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0002T0006Z000C1N2_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>87.01801345734451</v>
+        <v>14.14042718681848</v>
       </c>
       <c r="D2" t="n">
-        <v>13.71488859363438</v>
+        <v>2.228669396465587</v>
       </c>
       <c r="E2" t="n">
-        <v>14.39061763562216</v>
+        <v>2.338475365788601</v>
       </c>
       <c r="F2" t="n">
-        <v>17.39216201955586</v>
+        <v>2.826226328177827</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>59.60472758203051</v>
+        <v>9.685768232079958</v>
       </c>
       <c r="D3" t="n">
-        <v>17.06104840974041</v>
+        <v>2.772420366582816</v>
       </c>
       <c r="E3" t="n">
-        <v>14.39061763562216</v>
+        <v>2.338475365788601</v>
       </c>
       <c r="F3" t="n">
-        <v>17.39216201955586</v>
+        <v>2.826226328177827</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>36.97941787456399</v>
+        <v>6.009155404616649</v>
       </c>
       <c r="D4" t="n">
-        <v>38.07846744872432</v>
+        <v>6.187750960417702</v>
       </c>
       <c r="E4" t="n">
-        <v>14.39061763562216</v>
+        <v>2.338475365788601</v>
       </c>
       <c r="F4" t="n">
-        <v>17.39216201955586</v>
+        <v>2.826226328177827</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>57.46370971185458</v>
+        <v>9.33785282817637</v>
       </c>
       <c r="D5" t="n">
-        <v>28.75411923254658</v>
+        <v>4.672544375288819</v>
       </c>
       <c r="E5" t="n">
-        <v>14.39061763562216</v>
+        <v>2.338475365788601</v>
       </c>
       <c r="F5" t="n">
-        <v>17.39216201955586</v>
+        <v>2.826226328177827</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>40.05446516468637</v>
+        <v>6.508850589261535</v>
       </c>
       <c r="D6" t="n">
-        <v>31.01612483854165</v>
+        <v>5.040120286263018</v>
       </c>
       <c r="E6" t="n">
-        <v>14.39061763562216</v>
+        <v>2.338475365788601</v>
       </c>
       <c r="F6" t="n">
-        <v>17.39216201955586</v>
+        <v>2.826226328177827</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>50.48246942274697</v>
+        <v>8.203401281196383</v>
       </c>
       <c r="D7" t="n">
-        <v>26</v>
+        <v>4.225000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>14.39061763562216</v>
+        <v>2.338475365788601</v>
       </c>
       <c r="F7" t="n">
-        <v>17.39216201955586</v>
+        <v>2.826226328177827</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>72.36443179201852</v>
+        <v>11.75922016620301</v>
       </c>
       <c r="D8" t="n">
-        <v>69.95482364448631</v>
+        <v>11.36765884222903</v>
       </c>
       <c r="E8" t="n">
-        <v>14.39061763562216</v>
+        <v>2.338475365788601</v>
       </c>
       <c r="F8" t="n">
-        <v>17.39216201955586</v>
+        <v>2.826226328177827</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>66.16707848257616</v>
+        <v>10.75215025341863</v>
       </c>
       <c r="D9" t="n">
-        <v>63.50092979421682</v>
+        <v>10.31890109156023</v>
       </c>
       <c r="E9" t="n">
-        <v>14.39061763562216</v>
+        <v>2.338475365788601</v>
       </c>
       <c r="F9" t="n">
-        <v>17.39216201955586</v>
+        <v>2.826226328177827</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>74.50293932949877</v>
+        <v>12.10672764104355</v>
       </c>
       <c r="D10" t="n">
-        <v>28.98849849479442</v>
+        <v>4.710631005404093</v>
       </c>
       <c r="E10" t="n">
-        <v>14.39061763562216</v>
+        <v>2.338475365788601</v>
       </c>
       <c r="F10" t="n">
-        <v>17.39216201955586</v>
+        <v>2.826226328177827</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>41.59375766621663</v>
+        <v>6.758985620760201</v>
       </c>
       <c r="D11" t="n">
-        <v>27.95371413818834</v>
+        <v>4.542478547455606</v>
       </c>
       <c r="E11" t="n">
-        <v>14.39061763562216</v>
+        <v>2.338475365788601</v>
       </c>
       <c r="F11" t="n">
-        <v>17.39216201955586</v>
+        <v>2.826226328177827</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>57.54412894665563</v>
+        <v>9.35092095383154</v>
       </c>
       <c r="D12" t="n">
-        <v>54.93286689035394</v>
+        <v>8.926590869682515</v>
       </c>
       <c r="E12" t="n">
-        <v>14.39061763562216</v>
+        <v>2.338475365788601</v>
       </c>
       <c r="F12" t="n">
-        <v>17.39216201955586</v>
+        <v>2.826226328177827</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>55.56627346627189</v>
+        <v>9.029519438269181</v>
       </c>
       <c r="D13" t="n">
-        <v>21.12650796821772</v>
+        <v>3.433057544835379</v>
       </c>
       <c r="E13" t="n">
-        <v>14.39061763562216</v>
+        <v>2.338475365788601</v>
       </c>
       <c r="F13" t="n">
-        <v>17.39216201955586</v>
+        <v>2.826226328177827</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
